--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:45</t>
+    <t xml:space="preserve">2026-10-05 10:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -687,7 +687,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>653183.12</v>
+        <v>653183.13</v>
       </c>
     </row>
     <row r="10">
@@ -721,7 +721,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>620237.62</v>
+        <v>620237.63</v>
       </c>
     </row>
     <row r="12">
@@ -925,7 +925,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>546983.62</v>
+        <v>546983.63</v>
       </c>
     </row>
     <row r="24">
